--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -15921,6 +15921,408 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15954,7 +16356,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16439,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -16047,7 +16449,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -16067,7 +16469,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1014,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1164,9 +1161,6 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1416,7 +1410,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1566,9 +1560,6 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1818,7 +1809,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1968,9 +1959,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2220,7 +2208,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2370,9 +2358,6 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2622,7 +2607,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2772,9 +2757,6 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3024,7 +3006,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3171,9 +3153,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3420,7 +3399,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3570,9 +3549,6 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3822,7 +3798,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3972,9 +3948,6 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4224,7 +4197,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4374,9 +4347,6 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4626,7 +4596,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4776,9 +4746,6 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5028,7 +4995,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5175,9 +5142,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5424,7 +5388,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5574,9 +5538,6 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5826,7 +5787,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -5976,9 +5937,6 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6228,7 +6186,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6378,9 +6336,6 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6630,7 +6585,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6780,9 +6735,6 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7032,7 +6984,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7179,9 +7131,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7428,7 +7377,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7578,9 +7527,6 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7830,7 +7776,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -7980,9 +7926,6 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8232,7 +8175,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8382,9 +8325,6 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8634,7 +8574,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8784,9 +8724,6 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -9036,7 +8973,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9183,9 +9120,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9432,7 +9366,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9582,9 +9516,6 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9834,7 +9765,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9984,9 +9915,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -10236,7 +10164,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10386,9 +10314,6 @@
       <c r="P50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10638,7 +10563,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10788,9 +10713,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -11040,7 +10962,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11190,9 +11112,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11442,7 +11361,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11589,9 +11508,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11838,7 +11754,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11988,9 +11904,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -12240,7 +12153,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12390,9 +12303,6 @@
       <c r="P60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12642,7 +12552,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12792,9 +12702,6 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13044,7 +12951,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,9 +13101,6 @@
       <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -13446,7 +13350,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13593,9 +13497,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13842,7 +13743,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13992,9 +13893,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -14244,7 +14142,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14394,9 +14292,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14646,7 +14541,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14796,9 +14691,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -15048,7 +14940,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15198,9 +15090,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -15450,7 +15339,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15597,9 +15486,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15846,7 +15732,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15996,9 +15882,6 @@
       <c r="P78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -16248,7 +16131,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -16206,6 +16206,405 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16239,7 +16638,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16721,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -16332,7 +16731,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -16352,7 +16751,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -16605,6 +16605,405 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16638,7 +17037,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16721,7 +17120,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -16731,7 +17130,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -16751,7 +17150,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26755,7 +26755,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29527,7 +29527,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26755,7 +26755,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29527,7 +29527,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26755,7 +26755,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29527,7 +29527,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -30006,6 +30006,1192 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Nipah</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>@니파바이러스감염증</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Korea KDCA Nipah virus infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30039,7 +31225,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -30122,7 +31308,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -30132,7 +31318,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -30152,7 +31338,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
